--- a/printables/gift-budget-tracker/out/Christmas-Gift-Budget-Tracker-Example.xlsx
+++ b/printables/gift-budget-tracker/out/Christmas-Gift-Budget-Tracker-Example.xlsx
@@ -774,7 +774,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Quiet Table Co.  ·  Excel + Google Sheets  ·  Made for one household, for personal use</t>
+          <t>Pantry Printable Co.  ·  Excel + Google Sheets  ·  Made for one household, for personal use</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -931,7 +931,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Merry Christmas from Quiet Table Co.</t>
+          <t>Merry Christmas from Pantry Printable Co.</t>
         </is>
       </c>
     </row>
